--- a/data/trans_orig/P04A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04A_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la vivienda que ocupan es de propiedad o de alquiler en 2023</t>
+          <t>Población según si la vivienda que ocupan es de propiedad o de alquiler en 2023 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35363</t>
+          <t>33977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>13510</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>9563</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38968</t>
+          <t>40092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>9463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26056</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27453</t>
+          <t>28265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>24214</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49579</t>
+          <t>48280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28852</t>
+          <t>28078</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56122</t>
+          <t>56006</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41727</t>
+          <t>42732</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>240762</t>
+          <t>251099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80060</t>
+          <t>80628</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>289880</t>
+          <t>295647</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38772</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66008</t>
+          <t>66063</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25657</t>
+          <t>24894</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44761</t>
+          <t>45220</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71335</t>
+          <t>68119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107174</t>
+          <t>103887</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93165</t>
+          <t>94719</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142973</t>
+          <t>145181</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100192</t>
+          <t>102634</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149993</t>
+          <t>149776</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>211141</t>
+          <t>212596</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>279762</t>
+          <t>283362</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>358523</t>
+          <t>356610</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>414578</t>
+          <t>411706</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>339266</t>
+          <t>331005</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>481033</t>
+          <t>479971</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>720384</t>
+          <t>717473</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>873637</t>
+          <t>873213</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,76%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>762</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12225</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24106</t>
+          <t>22949</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>8041</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19390</t>
+          <t>20400</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16973</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37234</t>
+          <t>37614</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49415</t>
+          <t>48136</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129419</t>
+          <t>130399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67534</t>
+          <t>68041</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101270</t>
+          <t>100626</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121673</t>
+          <t>121392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215756</t>
+          <t>215548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23157</t>
+          <t>22505</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76514</t>
+          <t>71800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33296</t>
+          <t>33078</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53563</t>
+          <t>54725</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62236</t>
+          <t>59097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118416</t>
+          <t>115627</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149385</t>
+          <t>150294</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>362174</t>
+          <t>364422</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>245109</t>
+          <t>244002</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>293408</t>
+          <t>293415</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>368862</t>
+          <t>345368</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>632985</t>
+          <t>630000</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>621095</t>
+          <t>616202</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>955077</t>
+          <t>928220</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>519531</t>
+          <t>516591</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>570897</t>
+          <t>571979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1161259</t>
+          <t>1172024</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1563889</t>
+          <t>1607816</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>21635</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26262</t>
+          <t>25062</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27615</t>
+          <t>30993</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9857</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35500</t>
+          <t>36864</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64383</t>
+          <t>66061</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107519</t>
+          <t>104909</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40077</t>
+          <t>39724</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>119602</t>
+          <t>116567</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106839</t>
+          <t>111470</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>201539</t>
+          <t>204826</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21397</t>
+          <t>20899</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>52620</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14260</t>
+          <t>13653</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46227</t>
+          <t>46460</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>38095</t>
+          <t>40742</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>87492</t>
+          <t>88843</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>171366</t>
+          <t>171957</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>229645</t>
+          <t>230903</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>97260</t>
+          <t>100869</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>265418</t>
+          <t>264969</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>253272</t>
+          <t>253740</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>468991</t>
+          <t>472920</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>335181</t>
+          <t>331874</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>396706</t>
+          <t>397027</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>491158</t>
+          <t>494284</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>766250</t>
+          <t>774220</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>859528</t>
+          <t>851742</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1205916</t>
+          <t>1215077</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,6%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26496</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21378</t>
+          <t>21874</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23518</t>
+          <t>22161</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>17728</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38135</t>
+          <t>38783</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>97155</t>
+          <t>98565</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>142923</t>
+          <t>143653</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>125755</t>
+          <t>126133</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>355053</t>
+          <t>373762</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>244365</t>
+          <t>246361</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>527292</t>
+          <t>534628</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>24960</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59705</t>
+          <t>58850</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18313</t>
+          <t>18542</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39006</t>
+          <t>39001</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49194</t>
+          <t>48205</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>89249</t>
+          <t>88931</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>190275</t>
+          <t>191482</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>244918</t>
+          <t>247699</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>190066</t>
+          <t>188082</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>266772</t>
+          <t>266920</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>402307</t>
+          <t>401279</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>497442</t>
+          <t>496126</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>495898</t>
+          <t>494908</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>561868</t>
+          <t>561374</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>507036</t>
+          <t>498375</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>670861</t>
+          <t>670956</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1006074</t>
+          <t>1009615</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1204595</t>
+          <t>1203783</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,69%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>17959</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>52531</t>
+          <t>57827</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>15216</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>36674</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>39112</t>
+          <t>37965</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>79225</t>
+          <t>78140</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>39627</t>
+          <t>39230</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>76586</t>
+          <t>75573</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>36734</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>63766</t>
+          <t>65679</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>83883</t>
+          <t>83018</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>128472</t>
+          <t>129157</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>256410</t>
+          <t>267033</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>387848</t>
+          <t>392469</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>340228</t>
+          <t>339552</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>712779</t>
+          <t>692543</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>667054</t>
+          <t>661637</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1046314</t>
+          <t>1017651</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>131457</t>
+          <t>128722</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>206495</t>
+          <t>206914</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>107363</t>
+          <t>107086</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>156850</t>
+          <t>159616</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>260405</t>
+          <t>256461</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>350632</t>
+          <t>346746</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>637886</t>
+          <t>637056</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>890894</t>
+          <t>899659</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>684918</t>
+          <t>651829</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>901030</t>
+          <t>906038</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1397476</t>
+          <t>1391446</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1771538</t>
+          <t>1756155</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1903297</t>
+          <t>1897379</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2344781</t>
+          <t>2328557</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2064087</t>
+          <t>2077064</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2481545</t>
+          <t>2508919</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4002936</t>
+          <t>4027311</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4603104</t>
+          <t>4626237</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04A_2023-Habitat-trans_orig.xlsx
@@ -725,102 +725,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15174</t>
+          <t>18999</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33977</t>
+          <t>40839</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6148</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13695</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>25146</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>12923</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>46361</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5190</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13510</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>20364</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>9563</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>40092</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9463</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26560</t>
+          <t>25709</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18576</t>
+          <t>19276</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>12324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28265</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>34625</t>
+          <t>35954</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>26167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48280</t>
+          <t>51180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40880</t>
+          <t>59477</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28078</t>
+          <t>45503</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56006</t>
+          <t>77776</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>91585</t>
+          <t>56085</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42732</t>
+          <t>43541</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>251099</t>
+          <t>70153</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>132465</t>
+          <t>115562</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80628</t>
+          <t>95735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>295647</t>
+          <t>140751</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -1064,102 +1064,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51415</t>
+          <t>51768</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39069</t>
+          <t>39087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66063</t>
+          <t>66238</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>36282</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>27487</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>46835</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>88049</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>74137</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>108267</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>6,23%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>35062</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>24894</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>45220</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>86477</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>68119</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>103887</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>117275</t>
+          <t>119910</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94719</t>
+          <t>98192</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>145181</t>
+          <t>148986</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>129735</t>
+          <t>137529</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102634</t>
+          <t>120649</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149776</t>
+          <t>157317</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>247011</t>
+          <t>257439</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212596</t>
+          <t>226627</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>283362</t>
+          <t>288235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>386094</t>
+          <t>417190</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>356610</t>
+          <t>388212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>411706</t>
+          <t>447020</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>441411</t>
+          <t>474514</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>331005</t>
+          <t>452430</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>479971</t>
+          <t>498978</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>827506</t>
+          <t>891704</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>717473</t>
+          <t>854289</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>873213</t>
+          <t>929085</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>65,71%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>626887</t>
+          <t>684021</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>626887</t>
+          <t>684021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>626887</t>
+          <t>684021</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>721559</t>
+          <t>729833</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>721559</t>
+          <t>729833</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>721559</t>
+          <t>729833</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1348447</t>
+          <t>1413854</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1348447</t>
+          <t>1413854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1348447</t>
+          <t>1413854</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>18332</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -1633,102 +1633,102 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13798</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>11994</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>29587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>15571</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10223</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>23352</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>34368</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>24553</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>46537</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12924</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>8041</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>20400</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>26722</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>16498</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>37614</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93042</t>
+          <t>140799</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48136</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130399</t>
+          <t>168719</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>82888</t>
+          <t>107632</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68041</t>
+          <t>90323</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100626</t>
+          <t>129153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>175930</t>
+          <t>248431</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121392</t>
+          <t>215780</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215548</t>
+          <t>280830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>48771</t>
+          <t>45546</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22505</t>
+          <t>31994</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71800</t>
+          <t>64378</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42230</t>
+          <t>44253</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33078</t>
+          <t>33226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54725</t>
+          <t>56595</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>91001</t>
+          <t>89800</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59097</t>
+          <t>71950</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115627</t>
+          <t>111225</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>277514</t>
+          <t>288861</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>150294</t>
+          <t>254154</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>364422</t>
+          <t>320561</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>267813</t>
+          <t>297042</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>244002</t>
+          <t>269625</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>293415</t>
+          <t>323569</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>545327</t>
+          <t>585903</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>345368</t>
+          <t>539279</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>630000</t>
+          <t>629165</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>747212</t>
+          <t>540603</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>616202</t>
+          <t>504972</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>928220</t>
+          <t>575746</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>545233</t>
+          <t>598237</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>516591</t>
+          <t>570234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>571979</t>
+          <t>629158</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1292445</t>
+          <t>1138840</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1172024</t>
+          <t>1092470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1607816</t>
+          <t>1187552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>56,35%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1184303</t>
+          <t>1039350</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1184303</t>
+          <t>1039350</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1184303</t>
+          <t>1039350</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>955413</t>
+          <t>1068041</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>955413</t>
+          <t>1068041</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>955413</t>
+          <t>1068041</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2139716</t>
+          <t>2107391</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2139716</t>
+          <t>2107391</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2139716</t>
+          <t>2107391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10425</t>
+          <t>12056</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21635</t>
+          <t>23911</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>18251</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25062</t>
+          <t>29905</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13456</t>
+          <t>14035</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>26512</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11517</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>18428</t>
+          <t>20043</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>11832</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36864</t>
+          <t>33973</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>83242</t>
+          <t>132444</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>66061</t>
+          <t>108440</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104909</t>
+          <t>158643</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>82468</t>
+          <t>128196</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39724</t>
+          <t>107971</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>116567</t>
+          <t>154059</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>165710</t>
+          <t>260640</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111470</t>
+          <t>230237</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>204826</t>
+          <t>296292</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33513</t>
+          <t>33297</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52620</t>
+          <t>50414</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30094</t>
+          <t>30306</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13653</t>
+          <t>21382</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46460</t>
+          <t>42752</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>63607</t>
+          <t>63604</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>40742</t>
+          <t>47771</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>88843</t>
+          <t>82835</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>200091</t>
+          <t>209570</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>171957</t>
+          <t>180451</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>230903</t>
+          <t>239091</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>196406</t>
+          <t>219054</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100869</t>
+          <t>194317</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>264969</t>
+          <t>242918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>396497</t>
+          <t>428624</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>253740</t>
+          <t>391042</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>472920</t>
+          <t>468655</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>366228</t>
+          <t>403134</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>331874</t>
+          <t>372088</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>397027</t>
+          <t>435774</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>604428</t>
+          <t>410602</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>494284</t>
+          <t>383032</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>774220</t>
+          <t>435847</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>970656</t>
+          <t>813736</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>851742</t>
+          <t>771241</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1215077</t>
+          <t>854363</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>53,23%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>700014</t>
+          <t>798675</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>700014</t>
+          <t>798675</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>700014</t>
+          <t>798675</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>928792</t>
+          <t>806222</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>928792</t>
+          <t>806222</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>928792</t>
+          <t>806222</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1628806</t>
+          <t>1604898</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1628806</t>
+          <t>1604898</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1628806</t>
+          <t>1604898</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26776</t>
+          <t>21590</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>14343</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29056</t>
+          <t>28578</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>12569</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21874</t>
+          <t>23690</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22161</t>
+          <t>23505</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>26246</t>
+          <t>28440</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17728</t>
+          <t>19632</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38783</t>
+          <t>40564</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>119979</t>
+          <t>165692</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>98565</t>
+          <t>140409</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>143653</t>
+          <t>195952</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>194081</t>
+          <t>164214</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>126133</t>
+          <t>141908</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>373762</t>
+          <t>187508</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>314060</t>
+          <t>329906</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>246361</t>
+          <t>293506</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>534628</t>
+          <t>364772</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>36610</t>
+          <t>32353</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24960</t>
+          <t>21635</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58850</t>
+          <t>47684</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>27628</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18542</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39001</t>
+          <t>37151</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>64237</t>
+          <t>59406</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>48205</t>
+          <t>45065</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>88931</t>
+          <t>75754</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>216532</t>
+          <t>221712</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>191482</t>
+          <t>195171</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>247699</t>
+          <t>249851</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>236635</t>
+          <t>247786</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>188082</t>
+          <t>226527</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>266920</t>
+          <t>274204</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>453167</t>
+          <t>469498</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>401279</t>
+          <t>433925</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>496126</t>
+          <t>508482</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>528496</t>
+          <t>543929</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>494908</t>
+          <t>508874</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>561374</t>
+          <t>579026</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>617472</t>
+          <t>658390</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>498375</t>
+          <t>628940</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>670956</t>
+          <t>687285</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1145968</t>
+          <t>1202320</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1009615</t>
+          <t>1155956</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1203783</t>
+          <t>1244138</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,13%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>923684</t>
+          <t>986923</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>923684</t>
+          <t>986923</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>923684</t>
+          <t>986923</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1092944</t>
+          <t>1116990</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1092944</t>
+          <t>1116990</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1092944</t>
+          <t>1116990</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2016628</t>
+          <t>2103913</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2016628</t>
+          <t>2103913</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2016628</t>
+          <t>2103913</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,102 +3905,102 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>32120</t>
+          <t>39095</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>17959</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>57827</t>
+          <t>62564</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>28695</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>19262</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>41562</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>67790</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>48737</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>92877</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>23392</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>15216</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>36674</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>55512</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>37965</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>78140</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -4018,67 +4018,67 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>55872</t>
+          <t>63589</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>39230</t>
+          <t>48329</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>75573</t>
+          <t>83436</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>55216</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>42578</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>70146</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>50149</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>37978</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>65679</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>106021</t>
+          <t>118804</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>83018</t>
+          <t>99346</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>129157</t>
+          <t>142069</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>337144</t>
+          <t>498412</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>267033</t>
+          <t>448695</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>392469</t>
+          <t>547089</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>451021</t>
+          <t>456126</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>339552</t>
+          <t>418028</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>692543</t>
+          <t>493718</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>788165</t>
+          <t>954538</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>661637</t>
+          <t>891772</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1017651</t>
+          <t>1019000</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>170309</t>
+          <t>162964</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>128722</t>
+          <t>135264</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>206914</t>
+          <t>192107</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>135013</t>
+          <t>137895</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>107086</t>
+          <t>118556</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>159616</t>
+          <t>158985</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>305322</t>
+          <t>300859</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>256461</t>
+          <t>265254</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>346746</t>
+          <t>335113</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>811412</t>
+          <t>840053</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>637056</t>
+          <t>782188</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>899659</t>
+          <t>900527</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>830589</t>
+          <t>901411</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>651829</t>
+          <t>852137</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>906038</t>
+          <t>947552</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1642001</t>
+          <t>1741464</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1391446</t>
+          <t>1670810</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1756155</t>
+          <t>1818976</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2028030</t>
+          <t>1904856</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1897379</t>
+          <t>1839438</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2328557</t>
+          <t>1970047</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2208544</t>
+          <t>2141743</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2077064</t>
+          <t>2088751</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2508919</t>
+          <t>2197717</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4236574</t>
+          <t>4046600</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4027311</t>
+          <t>3961917</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4626237</t>
+          <t>4131355</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3434888</t>
+          <t>3508969</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3434888</t>
+          <t>3508969</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3434888</t>
+          <t>3508969</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3698708</t>
+          <t>3721087</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3698708</t>
+          <t>3721087</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3698708</t>
+          <t>3721087</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>7133596</t>
+          <t>7230056</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7133596</t>
+          <t>7230056</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7133596</t>
+          <t>7230056</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
